--- a/msubsls_25_2_7326(Sheet 1).xlsx
+++ b/msubsls_25_2_7326(Sheet 1).xlsx
@@ -1,35 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\17. PETA\PETA\FOLDER TERBARU\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DASHBOARD SE\fasih-sm-scrapper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56F8937-22E5-46D5-949C-E07C7CA29920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279A65D3-8128-459E-9D96-0774B0648AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="msubsls_25_2_7326(Sheet 1)" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
